--- a/Ammoniak/Ammoniak_Sensitivität/Sensitivitäten.xlsx
+++ b/Ammoniak/Ammoniak_Sensitivität/Sensitivitäten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak_Sensitivität\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Ammoniak\Ammoniak_Sensitivität\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F4F4A8-5ABF-48E7-BB68-8F8E4E10C221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9FE5B3-D268-4037-8DEF-FA4B70CF2162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
   <si>
     <t>Wert</t>
   </si>
@@ -177,8 +177,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -247,26 +247,22 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -275,7 +271,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -557,11 +552,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.77734375" customWidth="1"/>
     <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
@@ -570,10 +565,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -584,165 +579,39 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
+        <v>1500</v>
+      </c>
+      <c r="C2">
         <v>1000</v>
       </c>
-      <c r="C2">
-        <f>$B2*Grenzen!A$2</f>
-        <v>800</v>
-      </c>
       <c r="D2">
-        <f>$B2*Grenzen!B$2</f>
-        <v>1200</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4">
-        <v>9070</v>
-      </c>
-      <c r="C3">
-        <f>$B3*Grenzen!A$2</f>
-        <v>7256</v>
-      </c>
-      <c r="D3">
-        <f>$B3*Grenzen!B$2</f>
-        <v>10884</v>
-      </c>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1990</v>
-      </c>
-      <c r="C4">
-        <f>$B4*Grenzen!A$2</f>
-        <v>1592</v>
-      </c>
-      <c r="D4">
-        <f>$B4*Grenzen!B$2</f>
-        <v>2388</v>
-      </c>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4">
-        <v>490</v>
-      </c>
-      <c r="C5">
-        <f>$B5*Grenzen!A$2</f>
-        <v>392</v>
-      </c>
-      <c r="D5">
-        <f>$B5*Grenzen!B$2</f>
-        <v>588</v>
-      </c>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4">
-        <f>B7*4</f>
-        <v>424</v>
-      </c>
-      <c r="C6">
-        <f>$B6*Grenzen!A$2</f>
-        <v>339.20000000000005</v>
-      </c>
-      <c r="D6">
-        <f>$B6*Grenzen!B$2</f>
-        <v>508.79999999999995</v>
-      </c>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="4">
-        <v>106</v>
-      </c>
-      <c r="C7">
-        <f>$B7*Grenzen!A$2</f>
-        <v>84.800000000000011</v>
-      </c>
-      <c r="D7">
-        <f>$B7*Grenzen!B$2</f>
-        <v>127.19999999999999</v>
-      </c>
+      <c r="B7" s="3"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1100</v>
-      </c>
-      <c r="C8">
-        <f>$B8*Grenzen!A$2</f>
-        <v>880</v>
-      </c>
-      <c r="D8">
-        <f>$B8*Grenzen!B$2</f>
-        <v>1320</v>
-      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1080</v>
-      </c>
-      <c r="C9">
-        <f>$B9*Grenzen!A$2</f>
-        <v>864</v>
-      </c>
-      <c r="D9">
-        <f>$B9*Grenzen!B$2</f>
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="5">
-        <v>-1.5</v>
-      </c>
-      <c r="C10">
-        <f>$B10*Grenzen!B$2</f>
-        <v>-1.7999999999999998</v>
-      </c>
-      <c r="D10">
-        <f>$B10*Grenzen!A$2</f>
-        <v>-1.2000000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="5">
-        <v>-0.8</v>
-      </c>
-      <c r="C11">
-        <f>$B11*Grenzen!B$2</f>
-        <v>-0.96</v>
-      </c>
-      <c r="D11">
-        <f>$B11*Grenzen!A$2</f>
-        <v>-0.64000000000000012</v>
-      </c>
+      <c r="B9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -761,131 +630,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="11"/>
+      <c r="D1" s="8"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="6"/>
+      <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="10"/>
+      <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="10"/>
+      <c r="B9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="10"/>
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="12" t="s">
         <v>18</v>
       </c>
       <c r="B14" t="s">
@@ -896,7 +755,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
+      <c r="A15" s="10"/>
       <c r="B15" t="s">
         <v>20</v>
       </c>
@@ -905,7 +764,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
+      <c r="A16" s="10"/>
       <c r="B16" t="s">
         <v>21</v>
       </c>
@@ -914,7 +773,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
+      <c r="A17" s="10"/>
       <c r="B17" t="s">
         <v>22</v>
       </c>
@@ -923,7 +782,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
+      <c r="A18" s="10"/>
       <c r="B18" t="s">
         <v>23</v>
       </c>
@@ -932,7 +791,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
+      <c r="A19" s="10"/>
       <c r="B19" t="s">
         <v>24</v>
       </c>
@@ -941,7 +800,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
+      <c r="A20" s="10"/>
       <c r="B20" t="s">
         <v>25</v>
       </c>
@@ -950,7 +809,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
+      <c r="A21" s="10"/>
       <c r="B21" t="s">
         <v>26</v>
       </c>
@@ -959,7 +818,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
+      <c r="A22" s="10"/>
       <c r="B22" t="s">
         <v>27</v>
       </c>
@@ -968,7 +827,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
+      <c r="A23" s="10"/>
       <c r="B23" t="s">
         <v>34</v>
       </c>
@@ -977,7 +836,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
+      <c r="A24" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Ammoniak/Ammoniak_Sensitivität/Sensitivitäten.xlsx
+++ b/Ammoniak/Ammoniak_Sensitivität/Sensitivitäten.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Ammoniak\Ammoniak_Sensitivität\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Sensitivität\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9FE5B3-D268-4037-8DEF-FA4B70CF2162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61467389-A7E7-4B2B-A609-23C63B3D8044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
-    <sheet name="MonteCarlo" sheetId="7" r:id="rId2"/>
-    <sheet name="Grenzen" sheetId="6" r:id="rId3"/>
+    <sheet name="Ergebnisse" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="143">
   <si>
     <t>Wert</t>
   </si>
@@ -49,6 +48,396 @@
     <t>capex_pem</t>
   </si>
   <si>
+    <t>lower bound</t>
+  </si>
+  <si>
+    <t>upper bound</t>
+  </si>
+  <si>
+    <t>Prozess</t>
+  </si>
+  <si>
+    <t>Inputs</t>
+  </si>
+  <si>
+    <t>Outputs</t>
+  </si>
+  <si>
+    <t>calc_lcoe_wka</t>
+  </si>
+  <si>
+    <t>calc_lcoe_pv</t>
+  </si>
+  <si>
+    <t>calc_lcoe_bat</t>
+  </si>
+  <si>
+    <t>calc_lcoe_mix</t>
+  </si>
+  <si>
+    <t>calc_lcoh_h2s</t>
+  </si>
+  <si>
+    <t>calc_lcoh_pem</t>
+  </si>
+  <si>
+    <t>calc_lcoh_h2</t>
+  </si>
+  <si>
+    <t>calc_lcon_asu</t>
+  </si>
+  <si>
+    <t>calc_lcof_hb</t>
+  </si>
+  <si>
+    <t>ct/kWh</t>
+  </si>
+  <si>
+    <t>ct/kWh Speichermenge</t>
+  </si>
+  <si>
+    <t>€/kg Speichermenge</t>
+  </si>
+  <si>
+    <t>€/kg</t>
+  </si>
+  <si>
+    <t>€/t</t>
+  </si>
+  <si>
+    <t>Einheit</t>
+  </si>
+  <si>
+    <t>calc_GuV</t>
+  </si>
+  <si>
+    <t>€/a</t>
+  </si>
+  <si>
+    <t>€/kW_el</t>
+  </si>
+  <si>
+    <t>€/kg_NH3</t>
+  </si>
+  <si>
+    <t>annuity_pem</t>
+  </si>
+  <si>
+    <t>result_pem_leistung</t>
+  </si>
+  <si>
+    <t>result_pem_flowsum_elin</t>
+  </si>
+  <si>
+    <t>result_pem_flowsum_h2out</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest_pem</t>
+  </si>
+  <si>
+    <t>calc_opex_fix_pem</t>
+  </si>
+  <si>
+    <t>calc_annuity_pem</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_pem</t>
+  </si>
+  <si>
+    <t>calc_cost_pem</t>
+  </si>
+  <si>
+    <t>annuity_hb</t>
+  </si>
+  <si>
+    <t>result_hb_flowsum_nh3out</t>
+  </si>
+  <si>
+    <t>result_hb_flowsum_h2in</t>
+  </si>
+  <si>
+    <t>result_hb_flowsum_n2in</t>
+  </si>
+  <si>
+    <t>result_hb_flowsum_elin</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest_hb</t>
+  </si>
+  <si>
+    <t>calc_opex_fix_hb</t>
+  </si>
+  <si>
+    <t>calc_annuity_hb</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_hb</t>
+  </si>
+  <si>
+    <t>calc_cost_hb</t>
+  </si>
+  <si>
+    <t>annuity_asu</t>
+  </si>
+  <si>
+    <t>result_asu_leistung</t>
+  </si>
+  <si>
+    <t>result_asu_flowsum_elin</t>
+  </si>
+  <si>
+    <t>result_asu_flowsum_n2out</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest_asu</t>
+  </si>
+  <si>
+    <t>calc_opex_fix_asu</t>
+  </si>
+  <si>
+    <t>calc_annuity_asu</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_asu</t>
+  </si>
+  <si>
+    <t>calc_cost_asu</t>
+  </si>
+  <si>
+    <t>annuity_h2s</t>
+  </si>
+  <si>
+    <t>result_h2s_kapa</t>
+  </si>
+  <si>
+    <t>result_h2s_flowsum_in</t>
+  </si>
+  <si>
+    <t>result_h2s_flowsum_out</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest_h2s</t>
+  </si>
+  <si>
+    <t>calc_opex_fix_h2s</t>
+  </si>
+  <si>
+    <t>calc_annuity_h2s</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_h2s</t>
+  </si>
+  <si>
+    <t>calc_cost_h2s</t>
+  </si>
+  <si>
+    <t>annuity_bat_leistung</t>
+  </si>
+  <si>
+    <t>annuity_bat_kapa</t>
+  </si>
+  <si>
+    <t>result_bat_kapa</t>
+  </si>
+  <si>
+    <t>result_bat_leistung</t>
+  </si>
+  <si>
+    <t>result_bat_flowsum_out</t>
+  </si>
+  <si>
+    <t>result_bat_flowsum_in</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest_bat</t>
+  </si>
+  <si>
+    <t>calc_opex_fix_bat</t>
+  </si>
+  <si>
+    <t>calc_annuity_bat</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_bat</t>
+  </si>
+  <si>
+    <t>calc_cost_bat</t>
+  </si>
+  <si>
+    <t>result_strombezug_flowsum</t>
+  </si>
+  <si>
+    <t>calc_strombezug_kosten</t>
+  </si>
+  <si>
+    <t>annuity_pv</t>
+  </si>
+  <si>
+    <t>result_pv_leistung</t>
+  </si>
+  <si>
+    <t>result_pv_flowsum_generation</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest_pv</t>
+  </si>
+  <si>
+    <t>calc_opex_fix_pv</t>
+  </si>
+  <si>
+    <t>calc_opex_var_pv</t>
+  </si>
+  <si>
+    <t>calc_annuity_pv</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_pv</t>
+  </si>
+  <si>
+    <t>calc_cost_pv</t>
+  </si>
+  <si>
+    <t>annuity_wkaon</t>
+  </si>
+  <si>
+    <t>result_wka_leistung</t>
+  </si>
+  <si>
+    <t>result_wka_flowsum_generation</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest_wka</t>
+  </si>
+  <si>
+    <t>calc_opex_fix_wkaon</t>
+  </si>
+  <si>
+    <t>calc_opex_var_wkaon</t>
+  </si>
+  <si>
+    <t>calc_annuity_wka</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_wka</t>
+  </si>
+  <si>
+    <t>calc_cost_wkaon</t>
+  </si>
+  <si>
+    <t>result_stromverkauf_flowsum</t>
+  </si>
+  <si>
+    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
+  </si>
+  <si>
+    <t>calc_einnahmen_stromverkauf</t>
+  </si>
+  <si>
+    <t>result_h2verkauf_flowsum</t>
+  </si>
+  <si>
+    <t>calc_einnahmen_h2verkauf</t>
+  </si>
+  <si>
+    <t>result_nh3verkauf_flowsum</t>
+  </si>
+  <si>
+    <t>calc_einnahmen_nh3verkauf</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_gesamt</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest</t>
+  </si>
+  <si>
+    <t>calc_opex_gesamt</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_annuity_gesamt</t>
+  </si>
+  <si>
+    <t>calc_einnahmen_gesamt</t>
+  </si>
+  <si>
+    <t>calc_ausgaben_gesamt</t>
+  </si>
+  <si>
+    <t>calc_cost_gesamt</t>
+  </si>
+  <si>
+    <t>calc_cost_el</t>
+  </si>
+  <si>
+    <t>calc_cost_h2</t>
+  </si>
+  <si>
+    <t>calc_cost_n2</t>
+  </si>
+  <si>
+    <t>calc_cost_nh3</t>
+  </si>
+  <si>
+    <t>calc_maxprice</t>
+  </si>
+  <si>
+    <t>calc_price</t>
+  </si>
+  <si>
+    <t>€/ kWa</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>MWh/a</t>
+  </si>
+  <si>
+    <t>kg_H2/a</t>
+  </si>
+  <si>
+    <t>€</t>
+  </si>
+  <si>
+    <t>€ h/ kg a</t>
+  </si>
+  <si>
+    <t>kg_NH3/a</t>
+  </si>
+  <si>
+    <t>kg_N2/a</t>
+  </si>
+  <si>
+    <t>kW_el</t>
+  </si>
+  <si>
+    <t>€/ kg a</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>€/ kWh a</t>
+  </si>
+  <si>
+    <t>kWh</t>
+  </si>
+  <si>
+    <t>capex_pv</t>
+  </si>
+  <si>
+    <t>€/kW</t>
+  </si>
+  <si>
+    <t>Farbe</t>
+  </si>
+  <si>
+    <t>col_pem</t>
+  </si>
+  <si>
+    <t>col_pv</t>
+  </si>
+  <si>
     <t>capex_hb</t>
   </si>
   <si>
@@ -58,118 +447,25 @@
     <t>capex_h2s</t>
   </si>
   <si>
-    <t>capex_pv</t>
+    <t>capex_bat_leistung</t>
   </si>
   <si>
     <t>capex_wkaon</t>
   </si>
   <si>
-    <t>capex_bat_leistung</t>
-  </si>
-  <si>
-    <t>capex_bat_kapa</t>
-  </si>
-  <si>
-    <t>wasserstofferloes</t>
-  </si>
-  <si>
-    <t>ammoniakerloes</t>
-  </si>
-  <si>
-    <t>lower bound [%]</t>
-  </si>
-  <si>
-    <t>upper bound [%]</t>
-  </si>
-  <si>
-    <t>lower bound</t>
-  </si>
-  <si>
-    <t>upper bound</t>
-  </si>
-  <si>
-    <t>Prozess</t>
-  </si>
-  <si>
-    <t>Inputs</t>
-  </si>
-  <si>
-    <t>Outputs</t>
-  </si>
-  <si>
-    <t>calc_lcoe_wka</t>
-  </si>
-  <si>
-    <t>calc_lcoe_pv</t>
-  </si>
-  <si>
-    <t>calc_lcoe_bat</t>
-  </si>
-  <si>
-    <t>calc_lcoe_mix</t>
-  </si>
-  <si>
-    <t>calc_lcoh_h2s</t>
-  </si>
-  <si>
-    <t>calc_lcoh_pem</t>
-  </si>
-  <si>
-    <t>calc_lcoh_h2</t>
-  </si>
-  <si>
-    <t>calc_lcon_asu</t>
-  </si>
-  <si>
-    <t>calc_lcof_hb</t>
-  </si>
-  <si>
-    <t>ct/kWh</t>
-  </si>
-  <si>
-    <t>ct/kWh Speichermenge</t>
-  </si>
-  <si>
-    <t>€/kg Speichermenge</t>
-  </si>
-  <si>
-    <t>€/kg</t>
-  </si>
-  <si>
-    <t>€/t</t>
-  </si>
-  <si>
-    <t>Einheit</t>
-  </si>
-  <si>
-    <t>calc_GuV</t>
-  </si>
-  <si>
-    <t>€/a</t>
-  </si>
-  <si>
-    <t>€/kW_el</t>
-  </si>
-  <si>
-    <t>€/kg_NH3 *h</t>
-  </si>
-  <si>
-    <t>€/kg_N2 *h</t>
-  </si>
-  <si>
-    <t>€/kg_H2 * h</t>
-  </si>
-  <si>
-    <t>€/kW</t>
-  </si>
-  <si>
-    <t>€/kWh</t>
-  </si>
-  <si>
-    <t>€/kg_H2</t>
-  </si>
-  <si>
-    <t>€/kg_NH3</t>
+    <t>col_hb</t>
+  </si>
+  <si>
+    <t>col_asu</t>
+  </si>
+  <si>
+    <t>col_h2s</t>
+  </si>
+  <si>
+    <t>col_bat</t>
+  </si>
+  <si>
+    <t>col_wka</t>
   </si>
 </sst>
 </file>
@@ -177,10 +473,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,12 +495,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -247,30 +537,33 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -552,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -564,7 +857,7 @@
     <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -572,45 +865,149 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="6">
         <v>1500</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="13">
+        <f>B2/1.5</f>
         <v>1000</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="13">
+        <f>B2/0.5</f>
         <v>3000</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1100</v>
+      </c>
+      <c r="C3" s="13">
+        <f t="shared" ref="C3:C8" si="0">B3/1.5</f>
+        <v>733.33333333333337</v>
+      </c>
+      <c r="D3" s="13">
+        <f t="shared" ref="D3:D8" si="1">B3/0.5</f>
+        <v>2200</v>
+      </c>
+      <c r="E3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="3">
+        <v>9070</v>
+      </c>
+      <c r="C4" s="13">
+        <f t="shared" si="0"/>
+        <v>6046.666666666667</v>
+      </c>
+      <c r="D4" s="13">
+        <f t="shared" si="1"/>
+        <v>18140</v>
+      </c>
+      <c r="E4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1990</v>
+      </c>
+      <c r="C5" s="13">
+        <f t="shared" si="0"/>
+        <v>1326.6666666666667</v>
+      </c>
+      <c r="D5" s="13">
+        <f t="shared" si="1"/>
+        <v>3980</v>
+      </c>
+      <c r="E5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="3">
+        <v>490</v>
+      </c>
+      <c r="C6" s="13">
+        <f t="shared" si="0"/>
+        <v>326.66666666666669</v>
+      </c>
+      <c r="D6" s="13">
+        <f t="shared" si="1"/>
+        <v>980</v>
+      </c>
+      <c r="E6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" s="3">
+        <v>424</v>
+      </c>
+      <c r="C7" s="13">
+        <f t="shared" si="0"/>
+        <v>282.66666666666669</v>
+      </c>
+      <c r="D7" s="13">
+        <f t="shared" si="1"/>
+        <v>848</v>
+      </c>
+      <c r="E7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1080</v>
+      </c>
+      <c r="C8" s="13">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="D8" s="13">
+        <f t="shared" si="1"/>
+        <v>2160</v>
+      </c>
+      <c r="E8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
     </row>
   </sheetData>
@@ -621,23 +1018,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF0969E-FF8D-4E07-84C2-402C85B868B8}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D1" s="8"/>
     </row>
@@ -646,234 +1043,989 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>17</v>
+      <c r="A3" s="9" t="s">
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="12"/>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="12"/>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="12"/>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="12"/>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="12"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="12"/>
+      <c r="B21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="12"/>
+      <c r="B22" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="12"/>
+      <c r="B23" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="C23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="12"/>
+      <c r="B24" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" t="s">
+      <c r="C24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="12"/>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="12"/>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="12"/>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="12"/>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="12"/>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="12"/>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="12"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="12"/>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="12"/>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="12"/>
+      <c r="B34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="12"/>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="12"/>
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="12"/>
+      <c r="B37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="12"/>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="12"/>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="12"/>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="12"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="12"/>
+      <c r="B42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="12"/>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="12"/>
+      <c r="B44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="12"/>
+      <c r="B45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="12"/>
+      <c r="B46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="12"/>
+      <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="12"/>
+      <c r="B48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="12"/>
+      <c r="B49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="12"/>
+      <c r="B50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="12"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="12"/>
+      <c r="B52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="12"/>
+      <c r="B53" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="12"/>
+      <c r="B54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="12"/>
+      <c r="B55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="12"/>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="12"/>
+      <c r="B57" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="12"/>
+      <c r="B58" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="12"/>
+      <c r="B59" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="12"/>
+      <c r="B60" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="12"/>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="12"/>
+      <c r="B62" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="12"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="12"/>
+      <c r="B64" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="12"/>
+      <c r="B65" t="s">
+        <v>76</v>
+      </c>
+      <c r="C65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="12"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="12"/>
+      <c r="B67" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="12"/>
+      <c r="B68" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="12"/>
+      <c r="B69" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="12"/>
+      <c r="B70" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="12"/>
+      <c r="B71" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="12"/>
+      <c r="B72" t="s">
+        <v>82</v>
+      </c>
+      <c r="C72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="12"/>
+      <c r="B73" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="12"/>
+      <c r="B74" t="s">
+        <v>84</v>
+      </c>
+      <c r="C74" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="12"/>
+      <c r="B75" t="s">
+        <v>85</v>
+      </c>
+      <c r="C75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="12"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="12"/>
+      <c r="B77" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="12"/>
+      <c r="B78" t="s">
+        <v>87</v>
+      </c>
+      <c r="C78" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="12"/>
+      <c r="B79" t="s">
+        <v>88</v>
+      </c>
+      <c r="C79" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="12"/>
+      <c r="B80" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="12"/>
+      <c r="B81" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="12"/>
+      <c r="B82" t="s">
+        <v>91</v>
+      </c>
+      <c r="C82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="12"/>
+      <c r="B83" t="s">
+        <v>92</v>
+      </c>
+      <c r="C83" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="12"/>
+      <c r="B84" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="12"/>
+      <c r="B85" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="12"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="12"/>
+      <c r="B87" t="s">
+        <v>95</v>
+      </c>
+      <c r="C87" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="12"/>
+      <c r="B88" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="12"/>
+      <c r="B89" t="s">
+        <v>97</v>
+      </c>
+      <c r="C89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="12"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="12"/>
+      <c r="B91" t="s">
+        <v>98</v>
+      </c>
+      <c r="C91" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="12"/>
+      <c r="B92" t="s">
+        <v>99</v>
+      </c>
+      <c r="C92" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="12"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="12"/>
+      <c r="B94" t="s">
+        <v>100</v>
+      </c>
+      <c r="C94" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="12"/>
+      <c r="B95" t="s">
+        <v>101</v>
+      </c>
+      <c r="C95" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="12"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="12"/>
+      <c r="B97" t="s">
+        <v>102</v>
+      </c>
+      <c r="C97" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="12"/>
+      <c r="B98" t="s">
+        <v>103</v>
+      </c>
+      <c r="C98" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="12"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="12"/>
+      <c r="B100" t="s">
+        <v>104</v>
+      </c>
+      <c r="C100" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="12"/>
+      <c r="B101" t="s">
+        <v>105</v>
+      </c>
+      <c r="C101" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="12"/>
+      <c r="B102" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="12"/>
+      <c r="B103" t="s">
+        <v>107</v>
+      </c>
+      <c r="C103" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="12"/>
+      <c r="B104" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="12"/>
+      <c r="B105" t="s">
+        <v>108</v>
+      </c>
+      <c r="C105" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="12"/>
+      <c r="B106" t="s">
         <v>8</v>
       </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" t="s">
+      <c r="C106" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="12"/>
+      <c r="B107" t="s">
         <v>9</v>
       </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
-      <c r="B11" t="s">
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="12"/>
+      <c r="B108" t="s">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" t="s">
+      <c r="C108" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="12"/>
+      <c r="B109" t="s">
         <v>11</v>
       </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C109" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="12"/>
+      <c r="B110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" t="s">
         <v>19</v>
       </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
-      <c r="B15" t="s">
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="12"/>
+      <c r="B111" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" t="s">
         <v>20</v>
       </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
-      <c r="B16" t="s">
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="12"/>
+      <c r="B112" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="12"/>
+      <c r="B113" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="12"/>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="s">
         <v>21</v>
       </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" t="s">
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="12"/>
+      <c r="B115" t="s">
+        <v>109</v>
+      </c>
+      <c r="C115" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="12"/>
+      <c r="B116" t="s">
+        <v>110</v>
+      </c>
+      <c r="C116" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="12"/>
+      <c r="B117" t="s">
+        <v>111</v>
+      </c>
+      <c r="C117" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="12"/>
+      <c r="B118" t="s">
+        <v>112</v>
+      </c>
+      <c r="C118" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="12"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="12"/>
+      <c r="B120" t="s">
+        <v>113</v>
+      </c>
+      <c r="C120" t="s">
         <v>26</v>
       </c>
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="10"/>
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
-      <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="12"/>
+      <c r="B121" t="s">
+        <v>114</v>
+      </c>
+      <c r="C121" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:A13"/>
-    <mergeCell ref="A14:A24"/>
+  <mergeCells count="1">
+    <mergeCell ref="A11:A121"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B1C43F3-B1DE-4E22-BF24-C80089CCAE00}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>0.8</v>
-      </c>
-      <c r="B2">
-        <v>1.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>